--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -42,6 +42,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dispatch_res_vintages" sheetId="33" state="visible" r:id="rId33"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dispatch_projection" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dispatch_tyndp" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dispatch_README" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -33574,6 +33575,306 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sheet</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>columns</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>commodities</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>commodity, year, price</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>EUR/MWh_th, EUR/t</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>annual fuel/EUA trajectories (monthly shape applied downstream)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>zone_basis</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>zone, hub</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>gas hub per zone (TTF / PSV / MIBGAS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>must_run</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>zone, tech, min_gen_frac</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>fraction</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>thermal must-run floors (CHP heat obligation etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>price_rules</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>zone, date_from, res_bid, price_floor</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>EUR/MWh</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>market rules per zone-period (IT/ES pre-reform 0-floors)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>res_schemes</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>zone, scheme, volume_share, bid_floor_eur_mwh, trigger_hours</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>share, EUR/MWh, h</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>RES subsidy bid tranches + paragraph-51-style triggers (FLEX: FR tranches repriced by the oa_ladder, triggers zeroed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>res_vintages</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>zone, tech, vintage_year, capacity_mw, scheme</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RES capacity by vintage/scheme, drives OA/CR expiry (20y support roll-off)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>projection</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>variable, annual_growth</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>pct/yr</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>structural CAGR fallbacks (demand, res, coal, lignite)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>tyndp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>zone, variable, year, value</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GW / TWh</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TYNDP capacity-demand trajectories incl. cap_flex_gw adequacy fleet</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>flex_costs (FLEX, absent=defaults)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>variable, year, value</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EUR/MWh, EUR/MW, fraction</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>c_mod=45 (revealed socle bid -40 =&gt; srmc-(-40)); c_start_&lt;class/tech&gt; (300-340 nuc, 20-90 fossil); u_commit_frac kappa=0.90 (scheduled commitment; kappa*alpha_op=0.67=observed fleet floor); alpha_band_op=0.74 (revealed socle share - fleet-operating band floor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>minstab (FLEX, absent=0)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>zone, year, value</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>grid-stability nuclear must-run P_minstab (C7) - CRE minimum-injection, 2026+ regime (0 for backtest years); availability-clamped in the LP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>reserves (FLEX, absent=defaults)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>variable, year, value</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>MW</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>r_up_req=1500 (committed headroom), r_down_req=1000 (footroom above technical minimum) - C6 fleet reserves</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>oa_ladder (FLEX, absent=defaults)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>variable, year, value</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>EUR/MWh</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>downward bid ladder: cr_bid=-1 (CR suspension instantaneous, encoded in the bid, trigger=0), oa_bid=-500 (legacy OA paid-regardless =&gt; market floor), mer_bid=-0.01 (merchant curtails just below zero; also the fired-tranche floor), market_floor=-500, market_cap=4000</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -29015,7 +29015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29701,6 +29701,99 @@
         </is>
       </c>
       <c r="G22" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>net_metering</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-500</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>salderingsregeling: rooftop PV netted at retail, never sees spot -&gt; price-insensitive (FiT-regardless analog); ~10 of ~35 GW RES</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sde</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-20</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SDE+/++ sliding premium (level: DE market_premium analog); Dutch negative-price rule = no subsidy in &gt;=6h negative runs -&gt; 6h trigger</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>merchant</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>subsidy-free offshore tenders (Borssele III/IV, Hollandse Kust) + PPA; curtails at 0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
         <is>
           <t>reference</t>
         </is>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -29015,7 +29015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29070,14 +29070,14 @@
         <v>0.3</v>
       </c>
       <c r="D2" t="n">
-        <v>-60</v>
+        <v>-300</v>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MaStR mix; EEG FiT paid regardless, §51 6h(2019)</t>
+          <t>EEG FiT paid regardless, pre-2016/small stock EXEMPT from par.51 -&gt; no trigger; depth measured 2025: ~44 GW solar still on at &lt;=-150, obs min -250 (right-censored)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -29132,14 +29132,14 @@
         <v>0.1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>post-EEG / merchant, curtails at 0</t>
+          <t>post-EEG / merchant; floor measured 2025 (576 neg h: p50 -2.0) — 0.0 pinned the boundary and starved the par.51 trigger runs</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -29249,21 +29249,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>green_certificate</t>
+          <t>gc_residential</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="D8" t="n">
-        <v>-80</v>
+        <v>-500</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flanders/Wallonia GC ~65-90 EUR/MWh, paid regardless</t>
+          <t>Flanders/Wallonia GC paid regardless (residential+legacy); measured 2025: solar yield 0.96 at &lt;=-150, 6.9 GW on at obs min -462 (right-censored -&gt; exchange-floor convention)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -29280,21 +29280,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>merchant</t>
+          <t>gc_offshore</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>merchant/CfD</t>
+          <t>offshore GC (~2.3 GW); measured 2025: wind_resp 1.15 through -150, halves below -&gt; certificate-value floor</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -29306,26 +29306,26 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>complement_remuneration</t>
+          <t>merchant</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="D10" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR stops at negative prices</t>
+          <t>merchant/CfD + responsive share; floor measured 2025 (519 neg h: p50 -2.7)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -29342,21 +29342,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>obligation_achat</t>
+          <t>complement_remuneration</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
       <c r="D11" t="n">
-        <v>-40</v>
+        <v>-5</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>OA FiT-like, paid regardless (older/small)</t>
+          <t>CR stops at negative prices</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -29373,21 +29373,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>merchant</t>
+          <t>obligation_achat</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>merchant/PPA</t>
+          <t>OA FiT-like, paid regardless (older/small)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -29399,26 +29399,26 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>roc</t>
+          <t>merchant</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D13" t="n">
-        <v>-45</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ROCs paid per MWh regardless</t>
+          <t>merchant/PPA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -29435,21 +29435,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cfd</t>
+          <t>roc</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="D14" t="n">
-        <v>-5</v>
+        <v>-45</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CfD 6h negative-price rule</t>
+          <t>ROCs paid per MWh regardless</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -29466,21 +29466,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>merchant</t>
+          <t>cfd</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>merchant</t>
+          <t>CfD 6h negative-price rule</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -29492,26 +29492,26 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>IT_NORTH</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cfd</t>
+          <t>merchant</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="D16" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FER1/CfD 6h rule</t>
+          <t>merchant</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -29528,21 +29528,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>merchant</t>
+          <t>cfd</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.65</v>
+        <v>0.35</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>merchant/PPA</t>
+          <t>FER1/CfD 6h rule</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -29554,26 +29554,26 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT_NORTH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>recore</t>
+          <t>merchant</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.3</v>
+        <v>0.65</v>
       </c>
       <c r="D18" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>RECORE</t>
+          <t>merchant/PPA</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -29590,21 +29590,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>merchant</t>
+          <t>recore</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>merchant/PPA</t>
+          <t>RECORE</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -29616,26 +29616,26 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>kev</t>
+          <t>merchant</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="D20" t="n">
-        <v>-50</v>
+        <v>-1</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pronovo KEV feed-in tariff, paid regardless</t>
+          <t>merchant/PPA; floor measured 2025 (546 neg h: p50 -1.0, obs mean -2.1; model 0.0-boundary artifact fixed)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -29652,21 +29652,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>merchant</t>
+          <t>kev</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>post-KEV / merchant</t>
+          <t>Pronovo KEV feed-in tariff, paid regardless</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -29678,26 +29678,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IT_NORTH</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>conto_energia</t>
+          <t>merchant</t>
         </is>
       </c>
       <c r="C22" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D22" t="n">
         <v>0</v>
-      </c>
-      <c r="D22" t="n">
-        <v>-70</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Conto Energia FiT paid regardless</t>
+          <t>post-KEV / merchant</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -29709,26 +29709,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>IT_NORTH</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>net_metering</t>
+          <t>conto_energia</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-500</v>
+        <v>-70</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>salderingsregeling: rooftop PV netted at retail, never sees spot -&gt; price-insensitive (FiT-regardless analog); ~10 of ~35 GW RES</t>
+          <t>Conto Energia FiT paid regardless</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -29745,21 +29745,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>sde</t>
+          <t>net_metering</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="D24" t="n">
-        <v>-20</v>
+        <v>-500</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SDE+/++ sliding premium (level: DE market_premium analog); Dutch negative-price rule = no subsidy in &gt;=6h negative runs -&gt; 6h trigger</t>
+          <t>salderingsregeling: rooftop PV netted at retail, never sees spot -&gt; price-insensitive (FiT-regardless analog); ~10 of ~35 GW RES</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -29776,24 +29776,55 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>sde</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-20</v>
+      </c>
+      <c r="E25" t="n">
+        <v>6</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>SDE+/++ sliding premium (level: DE market_premium analog); Dutch negative-price rule = no subsidy in &gt;=6h negative runs -&gt; 6h trigger</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>merchant</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C26" t="n">
         <v>0.15</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D26" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>subsidy-free offshore tenders (Borssele III/IV, Hollandse Kust) + PPA; curtails at 0</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>subsidy-free offshore tenders + PPA; floor measured 2025 (584 neg h: p50 -2.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
         <is>
           <t>reference</t>
         </is>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -43,6 +43,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dispatch_projection" sheetId="34" state="visible" r:id="rId34"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dispatch_tyndp" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dispatch_README" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dispatch_nuclear_newbuild" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -30429,7 +30430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D181"/>
+  <dimension ref="A1:D195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30541,7 +30542,7 @@
         <v>2025</v>
       </c>
       <c r="D6" t="n">
-        <v>61</v>
+        <v>64.01000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -30559,7 +30560,7 @@
         <v>2030</v>
       </c>
       <c r="D7" t="n">
-        <v>63</v>
+        <v>64.01000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -30577,7 +30578,7 @@
         <v>2040</v>
       </c>
       <c r="D8" t="n">
-        <v>55</v>
+        <v>50.529</v>
       </c>
     </row>
     <row r="9">
@@ -30595,7 +30596,7 @@
         <v>2050</v>
       </c>
       <c r="D9" t="n">
-        <v>50</v>
+        <v>17.712</v>
       </c>
     </row>
     <row r="10">
@@ -31693,7 +31694,7 @@
         <v>2025</v>
       </c>
       <c r="D70" t="n">
-        <v>4</v>
+        <v>2.077</v>
       </c>
     </row>
     <row r="71">
@@ -31711,7 +31712,7 @@
         <v>2030</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>2.077</v>
       </c>
     </row>
     <row r="72">
@@ -31729,7 +31730,7 @@
         <v>2040</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>2.077</v>
       </c>
     </row>
     <row r="73">
@@ -32125,7 +32126,7 @@
         <v>2025</v>
       </c>
       <c r="D94" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="95">
@@ -32143,7 +32144,7 @@
         <v>2030</v>
       </c>
       <c r="D95" t="n">
-        <v>3</v>
+        <v>2.595</v>
       </c>
     </row>
     <row r="96">
@@ -32161,7 +32162,7 @@
         <v>2040</v>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="97">
@@ -33061,7 +33062,7 @@
         <v>2025</v>
       </c>
       <c r="D146" t="n">
-        <v>7</v>
+        <v>7.398</v>
       </c>
     </row>
     <row r="147">
@@ -33079,7 +33080,7 @@
         <v>2030</v>
       </c>
       <c r="D147" t="n">
-        <v>5</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="148">
@@ -33692,6 +33693,258 @@
       </c>
       <c r="D181" t="n">
         <v>22</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.485</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0.485</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D190" t="n">
+        <v>64.01000000000001</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D191" t="n">
+        <v>5.943</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D192" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D193" t="n">
+        <v>7.398</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D194" t="n">
+        <v>8.349</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.485</v>
       </c>
     </row>
   </sheetData>
@@ -33999,6 +34252,185 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>zone</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>capacity_mw</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>commissioning_year</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>EPR2 Penly 1</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1670</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EPR2 Penly 2</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1670</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>EPR2 Gravelines 1</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1670</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2041</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>EPR2 Gravelines 2</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1670</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2043</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EPR2 Bugey 1</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1670</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2044</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>EPR2 Bugey 2</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1670</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2046</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -30430,7 +30430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D195"/>
+  <dimension ref="A1:D247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33945,6 +33945,942 @@
       </c>
       <c r="D195" t="n">
         <v>0.485</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D196" t="n">
+        <v>6.642</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D197" t="n">
+        <v>3.369</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D198" t="n">
+        <v>3.796</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D199" t="n">
+        <v>84.90000000000001</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D200" t="n">
+        <v>63.4</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>cap_coal_gw</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D201" t="n">
+        <v>25.293</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D202" t="n">
+        <v>31.745</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>cap_lignite_gw</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D203" t="n">
+        <v>21.205</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D204" t="n">
+        <v>45.435</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D205" t="n">
+        <v>59.339</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D206" t="n">
+        <v>502.5</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>cap_coal_gw</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D207" t="n">
+        <v>9.561</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D208" t="n">
+        <v>30.266</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D209" t="n">
+        <v>6.751</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D210" t="n">
+        <v>22.961</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D211" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>cap_coal_gw</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D212" t="n">
+        <v>3.966</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D213" t="n">
+        <v>11.952</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D214" t="n">
+        <v>8.188000000000001</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D215" t="n">
+        <v>13.61</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D216" t="n">
+        <v>467.2</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>IT_NORTH</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D217" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D218" t="n">
+        <v>64.01000000000001</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D219" t="n">
+        <v>64.01000000000001</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>2032</v>
+      </c>
+      <c r="D220" t="n">
+        <v>64.01000000000001</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D221" t="n">
+        <v>64.01000000000001</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D222" t="n">
+        <v>35.824</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D223" t="n">
+        <v>3.929</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D224" t="n">
+        <v>2.077</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>2032</v>
+      </c>
+      <c r="D225" t="n">
+        <v>2.077</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D226" t="n">
+        <v>2.077</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D228" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D229" t="n">
+        <v>2.96</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>2032</v>
+      </c>
+      <c r="D230" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D231" t="n">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D233" t="n">
+        <v>7.398</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D234" t="n">
+        <v>5.305</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>2032</v>
+      </c>
+      <c r="D235" t="n">
+        <v>2.153</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>2032</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.485</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.485</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>2032</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.485</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -30430,7 +30430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D247"/>
+  <dimension ref="A1:D265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30974,7 +30974,7 @@
         <v>2025</v>
       </c>
       <c r="D30" t="n">
-        <v>26</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="31">
@@ -30992,7 +30992,7 @@
         <v>2030</v>
       </c>
       <c r="D31" t="n">
-        <v>26</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="32">
@@ -31010,7 +31010,7 @@
         <v>2040</v>
       </c>
       <c r="D32" t="n">
-        <v>27</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="33">
@@ -31028,7 +31028,7 @@
         <v>2050</v>
       </c>
       <c r="D33" t="n">
-        <v>27</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="34">
@@ -32198,7 +32198,7 @@
         <v>2025</v>
       </c>
       <c r="D98" t="n">
-        <v>15</v>
+        <v>8.319000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -32216,7 +32216,7 @@
         <v>2030</v>
       </c>
       <c r="D99" t="n">
-        <v>15</v>
+        <v>8.319000000000001</v>
       </c>
     </row>
     <row r="100">
@@ -32234,7 +32234,7 @@
         <v>2040</v>
       </c>
       <c r="D100" t="n">
-        <v>16</v>
+        <v>9.319000000000001</v>
       </c>
     </row>
     <row r="101">
@@ -32252,7 +32252,7 @@
         <v>2050</v>
       </c>
       <c r="D101" t="n">
-        <v>16</v>
+        <v>9.319000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -34881,6 +34881,330 @@
       </c>
       <c r="D247" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D248" t="n">
+        <v>2.498</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>IT_NORTH</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D250" t="n">
+        <v>9.262499999999999</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>IT_NORTH</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.129</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>cap_psp_gw</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D252" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>cap_psp_gw</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D253" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>cap_psp_gw</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D254" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>cap_psp_gw</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D255" t="n">
+        <v>5.05</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>cap_psp_gw</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D256" t="n">
+        <v>6.681</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>cap_psp_gw</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D257" t="n">
+        <v>6.681</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>cap_psp_gw</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D258" t="n">
+        <v>6.681</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>cap_psp_gw</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D259" t="n">
+        <v>6.681</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D260" t="n">
+        <v>6.053</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>cap_psp_gw</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D261" t="n">
+        <v>6.641</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D262" t="n">
+        <v>5.317</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D263" t="n">
+        <v>20.302</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D264" t="n">
+        <v>19.234</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>cap_psp_gw</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D265" t="n">
+        <v>5.023</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -29016,7 +29016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29055,6 +29055,11 @@
           <t>scenario</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>year</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -29586,26 +29591,26 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>recore</t>
+          <t>kev</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
       <c r="D19" t="n">
-        <v>-10</v>
+        <v>-50</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>RECORE</t>
+          <t>Pronovo KEV feed-in tariff, paid regardless</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -29617,7 +29622,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -29626,17 +29631,17 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.7</v>
+        <v>0.25</v>
       </c>
       <c r="D20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>merchant/PPA; floor measured 2025 (546 neg h: p50 -1.0, obs mean -2.1; model 0.0-boundary artifact fixed)</t>
+          <t>post-KEV / merchant</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -29648,26 +29653,26 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>IT_NORTH</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>kev</t>
+          <t>conto_energia</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-50</v>
+        <v>-70</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Pronovo KEV feed-in tariff, paid regardless</t>
+          <t>Conto Energia FiT paid regardless</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -29679,26 +29684,26 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>merchant</t>
+          <t>net_metering</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>post-KEV / merchant</t>
+          <t>salderingsregeling: rooftop PV netted at retail, never sees spot -&gt; price-insensitive (FiT-regardless analog); ~10 of ~35 GW RES</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -29710,26 +29715,26 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>IT_NORTH</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>conto_energia</t>
+          <t>sde</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="D23" t="n">
-        <v>-70</v>
+        <v>-20</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Conto Energia FiT paid regardless</t>
+          <t>SDE+/++ sliding premium (level: DE market_premium analog); Dutch negative-price rule = no subsidy in &gt;=6h negative runs -&gt; 6h trigger</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -29746,21 +29751,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>net_metering</t>
+          <t>merchant</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="D24" t="n">
-        <v>-500</v>
+        <v>-2</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>salderingsregeling: rooftop PV netted at retail, never sees spot -&gt; price-insensitive (FiT-regardless analog); ~10 of ~35 GW RES</t>
+          <t>subsidy-free offshore tenders + PPA; floor measured 2025 (584 neg h: p50 -2.5)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -29772,38 +29777,41 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>sde</t>
+          <t>recore</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.55</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SDE+/++ sliding premium (level: DE market_premium analog); Dutch negative-price rule = no subsidy in &gt;=6h negative runs -&gt; 6h trigger</t>
+          <t>measured 2022: no negative hours observed -&gt; nothing bids below zero</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>reference</t>
         </is>
+      </c>
+      <c r="H25" t="n">
+        <v>2022</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -29812,23 +29820,230 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.15</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>subsidy-free offshore tenders + PPA; floor measured 2025 (584 neg h: p50 -2.5)</t>
+          <t>measured 2022: no negative hours observed -&gt; nothing bids below zero</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>reference</t>
         </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2022</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>recore</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>measured 2023: no negative hours observed -&gt; nothing bids below zero</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>merchant</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>measured 2023: no negative hours observed -&gt; nothing bids below zero</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>recore</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>measured 2024: 247 neg h (2.81% of hours), p50 -0.10, p10 -1.01, min -2.00; below-zero share = net-load quantile at the observed negative frequency</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>merchant</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.831</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>measured 2024: 247 neg h (2.81% of hours), p50 -0.10, p10 -1.01, min -2.00; below-zero share = net-load quantile at the observed negative frequency</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>recore</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="D31" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>measured 2025: 556 neg h (6.35% of hours), p50 -1.00, p10 -5.80, min -15.00; below-zero share = net-load quantile at the observed negative frequency</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>merchant</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>measured 2025: 556 neg h (6.35% of hours), p50 -1.00, p10 -5.80, min -15.00; below-zero share = net-load quantile at the observed negative frequency</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>2025</v>
       </c>
     </row>
   </sheetData>
@@ -30430,7 +30645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D265"/>
+  <dimension ref="A1:D280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32342,7 +32557,7 @@
         <v>2025</v>
       </c>
       <c r="D106" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="107">
@@ -32360,7 +32575,7 @@
         <v>2030</v>
       </c>
       <c r="D107" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108">
@@ -32702,7 +32917,7 @@
         <v>2025</v>
       </c>
       <c r="D126" t="n">
-        <v>3</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="127">
@@ -32720,7 +32935,7 @@
         <v>2030</v>
       </c>
       <c r="D127" t="n">
-        <v>6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="128">
@@ -32738,7 +32953,7 @@
         <v>2040</v>
       </c>
       <c r="D128" t="n">
-        <v>10</v>
+        <v>0.499</v>
       </c>
     </row>
     <row r="129">
@@ -32756,7 +32971,7 @@
         <v>2050</v>
       </c>
       <c r="D129" t="n">
-        <v>14</v>
+        <v>0.701</v>
       </c>
     </row>
     <row r="130">
@@ -35205,6 +35420,276 @@
       </c>
       <c r="D265" t="n">
         <v>5.023</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D266" t="n">
+        <v>29.28</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D267" t="n">
+        <v>29.4</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D268" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D269" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D270" t="n">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D271" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D272" t="n">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D273" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D274" t="n">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D275" t="n">
+        <v>152.2</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D276" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D277" t="n">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D278" t="n">
+        <v>7.226</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D279" t="n">
+        <v>4.484</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D280" t="n">
+        <v>113.9</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -29786,7 +29786,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -29820,7 +29820,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -29854,7 +29854,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -29888,7 +29888,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0.38</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -29922,7 +29922,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.169</v>
+        <v>0.62</v>
       </c>
       <c r="D29" t="n">
         <v>-1.01</v>
@@ -29956,7 +29956,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.831</v>
+        <v>0.38</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -29990,7 +29990,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.303</v>
+        <v>0.62</v>
       </c>
       <c r="D31" t="n">
         <v>-5.8</v>
@@ -30024,7 +30024,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.697</v>
+        <v>0.38</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -44,6 +44,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dispatch_tyndp" sheetId="35" state="visible" r:id="rId35"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dispatch_README" sheetId="36" state="visible" r:id="rId36"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dispatch_nuclear_newbuild" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dispatch_ntc_newbuild" sheetId="38" state="visible" r:id="rId38"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36176,6 +36177,1228 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>border</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>capacity_mw</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>commissioning_year</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DE_LU-BE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ALEGrO</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2019 249/312 -&gt; 2022 1164/1298; first DE-BE link, border was AC-coupled only before</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FR-GB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>IFA2</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FR-GB 2019 2036 -&gt; 2022 3071</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FR-GB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ElecLink</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FR-GB 2022 3071 -&gt; 2023 4087</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FR-IT_NORTH</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Savoie-Piemont</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FR-&gt;IT 2019 3563 -&gt; 2024 4554; half capacity 2022-11, full 2023-08 (RTE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>DK-GB</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Viking Link</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>built</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DK-GB 2022 0/0 -&gt; 2023 1408/1454</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FR-ES</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bay of Biscay (Golfe de Gascogne)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>2200</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>INELFE (RTE/REE) + EIB EUR 1.6 bn 2025; doubles FR-ES to 5000 MW. Corroborated by TYNDP 2024 reference grid ES00-FR00 = 5000/5000, i.e. today's 2800 + 2200</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CH-AT_SI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>DE_LU-AT_SI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DE_LU-AT_SI</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>IT_NORTH-AT_SI</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>IT_NORTH-AT_SI</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2035</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>500</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>IT_NORTH-AT_SI</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DE_LU-BE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D14" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DE_LU-BE</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FR-BE</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FR-BE</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BE-GB</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2035</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BE-GB</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BE-NL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BE-NL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2035</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DE_LU-CH</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DE_LU-CH</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2035</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>300</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>DE_LU-CH</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FR-CH</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CH-IT_NORTH</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>CH-IT_NORTH</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2035</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DE_LU-DK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DE_LU-DK</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>FR-DE_LU</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DE_LU-NL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D31" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DE_LU-NL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2035</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D32" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DE_LU-NL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DE_LU-PL_CZ</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>7000</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DK-GB</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2035</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1400</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>FR-ES</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>FR-ES</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ES-PT</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>FR-GB</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2035</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1250</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>FR-GB</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2040</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2600</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FR-IT_NORTH</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NL-GB</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>IT_NORTH-IT_SOUTH</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TYNDP 2024 candidate 2030</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>4000</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>tyndp_candidate</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ENTSO-E TYNDP 2024, sheet '3. Elec Invest Candidates'</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -6302,7 +6302,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>103.3333</v>
+        <v>104.3333</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>106.6667</v>
+        <v>109.6667</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>108.3333</v>
+        <v>112.3333</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>111.6667</v>
+        <v>117.6667</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>113.3333</v>
+        <v>120.3333</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>116.6667</v>
+        <v>125.6667</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>118.3333</v>
+        <v>128.3333</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>121.6667</v>
+        <v>133.6667</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>123.3333</v>
+        <v>136.3333</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>126.6667</v>
+        <v>141.6667</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>128.3333</v>
+        <v>144.3333</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>131.6667</v>
+        <v>149.6667</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>133.3333</v>
+        <v>152.3333</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>100</v>
+        <v>99.71429999999999</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>100.9524</v>
+        <v>101.2381</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>101.4286</v>
+        <v>102</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>101.9048</v>
+        <v>102.762</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>102.381</v>
+        <v>103.5239</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>102.8571</v>
+        <v>104.2856</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>103.3333</v>
+        <v>105.0476</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>103.8095</v>
+        <v>105.8095</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>104.2857</v>
+        <v>106.5714</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>104.7619</v>
+        <v>107.3333</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>105.2381</v>
+        <v>108.0952</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>105.7143</v>
+        <v>108.8572</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>106.1905</v>
+        <v>109.6191</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>106.6667</v>
+        <v>110.381</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>107.1429</v>
+        <v>111.1429</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>107.619</v>
+        <v>111.9047</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>108.0952</v>
+        <v>112.6666</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>108.5714</v>
+        <v>113.4285</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>109.0476</v>
+        <v>114.1904</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>109.5238</v>
+        <v>114.9524</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>110</v>
+        <v>115.7143</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>100</v>
+        <v>99.5714</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>101.4286</v>
+        <v>101.8572</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>102.1429</v>
+        <v>103.0001</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>102.8571</v>
+        <v>104.1428</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>103.5714</v>
+        <v>105.2857</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>104.2857</v>
+        <v>106.4285</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>105</v>
+        <v>107.5714</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>105.7143</v>
+        <v>108.7143</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>106.4286</v>
+        <v>109.8572</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>107.1429</v>
+        <v>111.0001</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>107.8571</v>
+        <v>112.1428</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>108.5714</v>
+        <v>113.2857</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>109.2857</v>
+        <v>114.4285</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>110</v>
+        <v>115.5714</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>110.7143</v>
+        <v>116.7143</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>111.4286</v>
+        <v>117.8572</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>112.1429</v>
+        <v>119.0001</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>112.8571</v>
+        <v>120.1428</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>113.5714</v>
+        <v>121.2857</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>114.2857</v>
+        <v>122.4285</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>115</v>
+        <v>123.5714</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>100</v>
+        <v>99.8571</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>100.4762</v>
+        <v>100.6191</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>100.7143</v>
+        <v>101</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>100.9524</v>
+        <v>101.381</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>101.1905</v>
+        <v>101.7619</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>101.4286</v>
+        <v>102.1429</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>101.6667</v>
+        <v>102.5239</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>101.9048</v>
+        <v>102.9048</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>102.1429</v>
+        <v>103.2858</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>102.381</v>
+        <v>103.6667</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>102.619</v>
+        <v>104.0475</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>102.8571</v>
+        <v>104.4285</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>103.0952</v>
+        <v>104.8095</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>103.3333</v>
+        <v>105.1904</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>103.5714</v>
+        <v>105.5714</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>103.8095</v>
+        <v>105.9523</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>104.0476</v>
+        <v>106.3333</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>104.2857</v>
+        <v>106.7143</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>104.5238</v>
+        <v>107.0952</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>104.7619</v>
+        <v>107.4762</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>105</v>
+        <v>107.8571</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4000000</v>
+        <v>3314285.7143</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5142857.1429</v>
+        <v>5828571.4287</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>5714285.7143</v>
+        <v>7085714.2858</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>6285714.2857</v>
+        <v>8342857.1429</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6857142.8571</v>
+        <v>9599999.9999</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7428571.4286</v>
+        <v>10857142.8572</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8000000</v>
+        <v>12114285.7143</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8571428.5714</v>
+        <v>13371428.5714</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9142857.142899999</v>
+        <v>14628571.4287</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9714285.714299999</v>
+        <v>15885714.2858</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10285714.2857</v>
+        <v>17142857.1429</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10857142.8571</v>
+        <v>18399999.9999</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11428571.4286</v>
+        <v>19657142.8572</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12000000</v>
+        <v>20914285.7143</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12571428.5714</v>
+        <v>22171428.5714</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13142857.1429</v>
+        <v>23428571.4287</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13714285.7143</v>
+        <v>24685714.2858</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14285714.2857</v>
+        <v>25942857.1429</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14857142.8571</v>
+        <v>27199999.9999</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15428571.4286</v>
+        <v>28457142.8572</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16000000</v>
+        <v>29714285.7143</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>100</v>
+        <v>99.6572</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -11449,7 +11449,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>101.1429</v>
+        <v>101.4858</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>101.7143</v>
+        <v>102.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>102.2857</v>
+        <v>103.3143</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>102.8571</v>
+        <v>104.2285</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>103.4286</v>
+        <v>105.1429</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>104</v>
+        <v>106.0572</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -11587,7 +11587,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>104.5714</v>
+        <v>106.9714</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>105.1429</v>
+        <v>107.8858</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -11633,7 +11633,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>105.7143</v>
+        <v>108.8</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>106.2857</v>
+        <v>109.7143</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>106.8571</v>
+        <v>110.6285</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>107.4286</v>
+        <v>111.5429</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>108</v>
+        <v>112.4572</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>108.5714</v>
+        <v>113.3714</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -11771,7 +11771,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>109.1429</v>
+        <v>114.2858</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>109.7143</v>
+        <v>115.2</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -11817,7 +11817,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>110.2857</v>
+        <v>116.1143</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -11840,7 +11840,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>110.8571</v>
+        <v>117.0285</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>111.4286</v>
+        <v>117.9429</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -11886,7 +11886,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>112</v>
+        <v>118.8572</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6667</v>
+        <v>0.667</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.2333</v>
+        <v>1.6253</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.8</v>
+        <v>2.5835</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.3667</v>
+        <v>3.5418</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.9333</v>
+        <v>4.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.0667</v>
+        <v>5.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.6333</v>
+        <v>6.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>5.2</v>
+        <v>7.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>5.7667</v>
+        <v>8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6.3333</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6.9</v>
+        <v>8.4</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7.4667</v>
+        <v>8.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8.033300000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9.7333</v>
+        <v>9.333299999999999</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.8667</v>
+        <v>9.666700000000001</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.4333</v>
+        <v>9.833299999999999</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>0.7619</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1.4762</v>
+        <v>1.7143</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1.7143</v>
+        <v>2.1905</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.9524</v>
+        <v>2.6667</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2.1905</v>
+        <v>3.1429</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2.4286</v>
+        <v>3.6191</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2.6667</v>
+        <v>4.0953</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2.9048</v>
+        <v>4.5715</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3.1429</v>
+        <v>5.0477</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>3.381</v>
+        <v>5.5239</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.619</v>
+        <v>5.9999</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3.8571</v>
+        <v>6.4761</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4.0952</v>
+        <v>6.9523</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4.3333</v>
+        <v>7.4285</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4.5714</v>
+        <v>7.9047</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4.8095</v>
+        <v>8.3809</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>5.0476</v>
+        <v>8.857100000000001</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5.2857</v>
+        <v>9.333299999999999</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5.5238</v>
+        <v>9.8095</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>5.7619</v>
+        <v>10.2857</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>6</v>
+        <v>10.7619</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>2025</v>
       </c>
       <c r="D2" t="n">
-        <v>9000</v>
+        <v>8940</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -21673,7 +21673,7 @@
         <v>2026</v>
       </c>
       <c r="D3" t="n">
-        <v>10476.19</v>
+        <v>11443.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -21696,7 +21696,7 @@
         <v>2027</v>
       </c>
       <c r="D4" t="n">
-        <v>11952.381</v>
+        <v>13946.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -21719,7 +21719,7 @@
         <v>2028</v>
       </c>
       <c r="D5" t="n">
-        <v>13428.571</v>
+        <v>16449.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>2029</v>
       </c>
       <c r="D6" t="n">
-        <v>14904.762</v>
+        <v>18952.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>2030</v>
       </c>
       <c r="D7" t="n">
-        <v>16380.952</v>
+        <v>21456</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>2031</v>
       </c>
       <c r="D8" t="n">
-        <v>17857.143</v>
+        <v>22797</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>2032</v>
       </c>
       <c r="D9" t="n">
-        <v>19333.333</v>
+        <v>24138</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -21834,7 +21834,7 @@
         <v>2033</v>
       </c>
       <c r="D10" t="n">
-        <v>20809.524</v>
+        <v>25479</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>2034</v>
       </c>
       <c r="D11" t="n">
-        <v>22285.714</v>
+        <v>26820</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>2035</v>
       </c>
       <c r="D12" t="n">
-        <v>23761.905</v>
+        <v>28161</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>2036</v>
       </c>
       <c r="D13" t="n">
-        <v>25238.095</v>
+        <v>29680.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>2037</v>
       </c>
       <c r="D14" t="n">
-        <v>26714.286</v>
+        <v>31200.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -21949,7 +21949,7 @@
         <v>2038</v>
       </c>
       <c r="D15" t="n">
-        <v>28190.476</v>
+        <v>32720.4</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>2039</v>
       </c>
       <c r="D16" t="n">
-        <v>29666.667</v>
+        <v>34240.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>2040</v>
       </c>
       <c r="D17" t="n">
-        <v>31142.857</v>
+        <v>35760</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>2041</v>
       </c>
       <c r="D18" t="n">
-        <v>32619.048</v>
+        <v>36877.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -22041,7 +22041,7 @@
         <v>2042</v>
       </c>
       <c r="D19" t="n">
-        <v>34095.238</v>
+        <v>37995</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>2043</v>
       </c>
       <c r="D20" t="n">
-        <v>35571.429</v>
+        <v>39112.5</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -22087,7 +22087,7 @@
         <v>2044</v>
       </c>
       <c r="D21" t="n">
-        <v>37047.619</v>
+        <v>40230</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>2045</v>
       </c>
       <c r="D22" t="n">
-        <v>38523.81</v>
+        <v>41347.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -22133,7 +22133,7 @@
         <v>2046</v>
       </c>
       <c r="D23" t="n">
-        <v>40000</v>
+        <v>42465</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -22156,7 +22156,7 @@
         <v>2025</v>
       </c>
       <c r="D24" t="n">
-        <v>7000</v>
+        <v>7060</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -22179,7 +22179,7 @@
         <v>2026</v>
       </c>
       <c r="D25" t="n">
-        <v>8190.476</v>
+        <v>9036.799999999999</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -22202,7 +22202,7 @@
         <v>2027</v>
       </c>
       <c r="D26" t="n">
-        <v>9380.951999999999</v>
+        <v>11013.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>2028</v>
       </c>
       <c r="D27" t="n">
-        <v>10571.429</v>
+        <v>12990.4</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>2029</v>
       </c>
       <c r="D28" t="n">
-        <v>11761.905</v>
+        <v>14967.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -22271,7 +22271,7 @@
         <v>2030</v>
       </c>
       <c r="D29" t="n">
-        <v>12952.381</v>
+        <v>16944</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>2031</v>
       </c>
       <c r="D30" t="n">
-        <v>14142.857</v>
+        <v>18003</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>2032</v>
       </c>
       <c r="D31" t="n">
-        <v>15333.333</v>
+        <v>19062</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>2033</v>
       </c>
       <c r="D32" t="n">
-        <v>16523.81</v>
+        <v>20121</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -22363,7 +22363,7 @@
         <v>2034</v>
       </c>
       <c r="D33" t="n">
-        <v>17714.286</v>
+        <v>21180</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>2035</v>
       </c>
       <c r="D34" t="n">
-        <v>18904.762</v>
+        <v>22239</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>2036</v>
       </c>
       <c r="D35" t="n">
-        <v>20095.238</v>
+        <v>23439.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>2037</v>
       </c>
       <c r="D36" t="n">
-        <v>21285.714</v>
+        <v>24639.4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>2038</v>
       </c>
       <c r="D37" t="n">
-        <v>22476.19</v>
+        <v>25839.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>2039</v>
       </c>
       <c r="D38" t="n">
-        <v>23666.667</v>
+        <v>27039.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>2040</v>
       </c>
       <c r="D39" t="n">
-        <v>24857.143</v>
+        <v>28240</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>2041</v>
       </c>
       <c r="D40" t="n">
-        <v>26047.619</v>
+        <v>29122.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>2042</v>
       </c>
       <c r="D41" t="n">
-        <v>27238.095</v>
+        <v>30005</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -22570,7 +22570,7 @@
         <v>2043</v>
       </c>
       <c r="D42" t="n">
-        <v>28428.571</v>
+        <v>30887.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -22593,7 +22593,7 @@
         <v>2044</v>
       </c>
       <c r="D43" t="n">
-        <v>29619.048</v>
+        <v>31770</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -22616,7 +22616,7 @@
         <v>2045</v>
       </c>
       <c r="D44" t="n">
-        <v>30809.524</v>
+        <v>32652.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>2046</v>
       </c>
       <c r="D45" t="n">
-        <v>32000</v>
+        <v>33535</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>2026</v>
       </c>
       <c r="D47" t="n">
-        <v>4666.667</v>
+        <v>5120</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -22708,7 +22708,7 @@
         <v>2027</v>
       </c>
       <c r="D48" t="n">
-        <v>5333.333</v>
+        <v>6240</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -22731,7 +22731,7 @@
         <v>2028</v>
       </c>
       <c r="D49" t="n">
-        <v>6000</v>
+        <v>7360</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>2029</v>
       </c>
       <c r="D50" t="n">
-        <v>6666.667</v>
+        <v>8480</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>2030</v>
       </c>
       <c r="D51" t="n">
-        <v>7333.333</v>
+        <v>9600</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -22800,7 +22800,7 @@
         <v>2031</v>
       </c>
       <c r="D52" t="n">
-        <v>8000</v>
+        <v>10200</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -22823,7 +22823,7 @@
         <v>2032</v>
       </c>
       <c r="D53" t="n">
-        <v>8666.666999999999</v>
+        <v>10800</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>2033</v>
       </c>
       <c r="D54" t="n">
-        <v>9333.333000000001</v>
+        <v>11400</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>2034</v>
       </c>
       <c r="D55" t="n">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>2035</v>
       </c>
       <c r="D56" t="n">
-        <v>10666.667</v>
+        <v>12600</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>2036</v>
       </c>
       <c r="D57" t="n">
-        <v>11333.333</v>
+        <v>13280</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>2037</v>
       </c>
       <c r="D58" t="n">
-        <v>12000</v>
+        <v>13960</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>2038</v>
       </c>
       <c r="D59" t="n">
-        <v>12666.667</v>
+        <v>14640</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>2039</v>
       </c>
       <c r="D60" t="n">
-        <v>13333.333</v>
+        <v>15320</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>2040</v>
       </c>
       <c r="D61" t="n">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>2041</v>
       </c>
       <c r="D62" t="n">
-        <v>14666.667</v>
+        <v>16500</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -23053,7 +23053,7 @@
         <v>2042</v>
       </c>
       <c r="D63" t="n">
-        <v>15333.333</v>
+        <v>17000</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -23076,7 +23076,7 @@
         <v>2043</v>
       </c>
       <c r="D64" t="n">
-        <v>16000</v>
+        <v>17500</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -23099,7 +23099,7 @@
         <v>2044</v>
       </c>
       <c r="D65" t="n">
-        <v>16666.667</v>
+        <v>18000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>2045</v>
       </c>
       <c r="D66" t="n">
-        <v>17333.333</v>
+        <v>18500</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>2046</v>
       </c>
       <c r="D67" t="n">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>2026</v>
       </c>
       <c r="D69" t="n">
-        <v>23095.238</v>
+        <v>23800</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -23214,7 +23214,7 @@
         <v>2027</v>
       </c>
       <c r="D70" t="n">
-        <v>24190.476</v>
+        <v>25600</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>2028</v>
       </c>
       <c r="D71" t="n">
-        <v>25285.714</v>
+        <v>27400</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -23260,7 +23260,7 @@
         <v>2029</v>
       </c>
       <c r="D72" t="n">
-        <v>26380.952</v>
+        <v>29200</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>2030</v>
       </c>
       <c r="D73" t="n">
-        <v>27476.19</v>
+        <v>31000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -23306,7 +23306,7 @@
         <v>2031</v>
       </c>
       <c r="D74" t="n">
-        <v>28571.429</v>
+        <v>32300</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>2032</v>
       </c>
       <c r="D75" t="n">
-        <v>29666.667</v>
+        <v>33600</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -23352,7 +23352,7 @@
         <v>2033</v>
       </c>
       <c r="D76" t="n">
-        <v>30761.905</v>
+        <v>34900</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>2034</v>
       </c>
       <c r="D77" t="n">
-        <v>31857.143</v>
+        <v>36200</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>2035</v>
       </c>
       <c r="D78" t="n">
-        <v>32952.381</v>
+        <v>37500</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>2036</v>
       </c>
       <c r="D79" t="n">
-        <v>34047.619</v>
+        <v>38400</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -23444,7 +23444,7 @@
         <v>2037</v>
       </c>
       <c r="D80" t="n">
-        <v>35142.857</v>
+        <v>39300</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -23467,7 +23467,7 @@
         <v>2038</v>
       </c>
       <c r="D81" t="n">
-        <v>36238.095</v>
+        <v>40200</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>2039</v>
       </c>
       <c r="D82" t="n">
-        <v>37333.333</v>
+        <v>41100</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>2040</v>
       </c>
       <c r="D83" t="n">
-        <v>38428.571</v>
+        <v>42000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -23536,7 +23536,7 @@
         <v>2041</v>
       </c>
       <c r="D84" t="n">
-        <v>39523.81</v>
+        <v>43000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -23559,7 +23559,7 @@
         <v>2042</v>
       </c>
       <c r="D85" t="n">
-        <v>40619.048</v>
+        <v>44000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -23582,7 +23582,7 @@
         <v>2043</v>
       </c>
       <c r="D86" t="n">
-        <v>41714.286</v>
+        <v>45000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -23605,7 +23605,7 @@
         <v>2044</v>
       </c>
       <c r="D87" t="n">
-        <v>42809.524</v>
+        <v>46000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -23628,7 +23628,7 @@
         <v>2045</v>
       </c>
       <c r="D88" t="n">
-        <v>43904.762</v>
+        <v>47000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>2046</v>
       </c>
       <c r="D89" t="n">
-        <v>45000</v>
+        <v>48000</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -23674,7 +23674,7 @@
         <v>2025</v>
       </c>
       <c r="D90" t="n">
-        <v>1500</v>
+        <v>1230</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -23697,7 +23697,7 @@
         <v>2026</v>
       </c>
       <c r="D91" t="n">
-        <v>2285.714</v>
+        <v>1574.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>2027</v>
       </c>
       <c r="D92" t="n">
-        <v>3071.429</v>
+        <v>1918.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>2028</v>
       </c>
       <c r="D93" t="n">
-        <v>3857.143</v>
+        <v>2263.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>2029</v>
       </c>
       <c r="D94" t="n">
-        <v>4642.857</v>
+        <v>2607.6</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -23789,7 +23789,7 @@
         <v>2030</v>
       </c>
       <c r="D95" t="n">
-        <v>5428.571</v>
+        <v>2952</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>2031</v>
       </c>
       <c r="D96" t="n">
-        <v>6214.286</v>
+        <v>4821.6</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>2032</v>
       </c>
       <c r="D97" t="n">
-        <v>7000</v>
+        <v>6691.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -23858,7 +23858,7 @@
         <v>2033</v>
       </c>
       <c r="D98" t="n">
-        <v>7785.714</v>
+        <v>8560.799999999999</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -23881,7 +23881,7 @@
         <v>2034</v>
       </c>
       <c r="D99" t="n">
-        <v>8571.429</v>
+        <v>10430.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>2035</v>
       </c>
       <c r="D100" t="n">
-        <v>9357.143</v>
+        <v>12300</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -23927,7 +23927,7 @@
         <v>2036</v>
       </c>
       <c r="D101" t="n">
-        <v>10142.857</v>
+        <v>12792</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>2037</v>
       </c>
       <c r="D102" t="n">
-        <v>10928.571</v>
+        <v>13284</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>2038</v>
       </c>
       <c r="D103" t="n">
-        <v>11714.286</v>
+        <v>13776</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -23996,7 +23996,7 @@
         <v>2039</v>
       </c>
       <c r="D104" t="n">
-        <v>12500</v>
+        <v>14268</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>2040</v>
       </c>
       <c r="D105" t="n">
-        <v>13285.714</v>
+        <v>14760</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -24042,7 +24042,7 @@
         <v>2041</v>
       </c>
       <c r="D106" t="n">
-        <v>14071.429</v>
+        <v>15306.7</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -24065,7 +24065,7 @@
         <v>2042</v>
       </c>
       <c r="D107" t="n">
-        <v>14857.143</v>
+        <v>15853.3</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>2043</v>
       </c>
       <c r="D108" t="n">
-        <v>15642.857</v>
+        <v>16400</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -24111,7 +24111,7 @@
         <v>2044</v>
       </c>
       <c r="D109" t="n">
-        <v>16428.571</v>
+        <v>16946.7</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>2045</v>
       </c>
       <c r="D110" t="n">
-        <v>17214.286</v>
+        <v>17493.3</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -24157,7 +24157,7 @@
         <v>2046</v>
       </c>
       <c r="D111" t="n">
-        <v>18000</v>
+        <v>18040</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>2025</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -24203,7 +24203,7 @@
         <v>2026</v>
       </c>
       <c r="D113" t="n">
-        <v>238.095</v>
+        <v>345.6</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -24226,7 +24226,7 @@
         <v>2027</v>
       </c>
       <c r="D114" t="n">
-        <v>476.19</v>
+        <v>421.2</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -24249,7 +24249,7 @@
         <v>2028</v>
       </c>
       <c r="D115" t="n">
-        <v>714.2859999999999</v>
+        <v>496.8</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>2029</v>
       </c>
       <c r="D116" t="n">
-        <v>952.381</v>
+        <v>572.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>2030</v>
       </c>
       <c r="D117" t="n">
-        <v>1190.476</v>
+        <v>648</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>2031</v>
       </c>
       <c r="D118" t="n">
-        <v>1428.571</v>
+        <v>1058.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>2032</v>
       </c>
       <c r="D119" t="n">
-        <v>1666.667</v>
+        <v>1468.8</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>2033</v>
       </c>
       <c r="D120" t="n">
-        <v>1904.762</v>
+        <v>1879.2</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>2034</v>
       </c>
       <c r="D121" t="n">
-        <v>2142.857</v>
+        <v>2289.6</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>2035</v>
       </c>
       <c r="D122" t="n">
-        <v>2380.952</v>
+        <v>2700</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -24433,7 +24433,7 @@
         <v>2036</v>
       </c>
       <c r="D123" t="n">
-        <v>2619.048</v>
+        <v>2808</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -24456,7 +24456,7 @@
         <v>2037</v>
       </c>
       <c r="D124" t="n">
-        <v>2857.143</v>
+        <v>2916</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>2038</v>
       </c>
       <c r="D125" t="n">
-        <v>3095.238</v>
+        <v>3024</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>2039</v>
       </c>
       <c r="D126" t="n">
-        <v>3333.333</v>
+        <v>3132</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -24525,7 +24525,7 @@
         <v>2040</v>
       </c>
       <c r="D127" t="n">
-        <v>3571.429</v>
+        <v>3240</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -24548,7 +24548,7 @@
         <v>2041</v>
       </c>
       <c r="D128" t="n">
-        <v>3809.524</v>
+        <v>3360</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -24571,7 +24571,7 @@
         <v>2042</v>
       </c>
       <c r="D129" t="n">
-        <v>4047.619</v>
+        <v>3480</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -24594,7 +24594,7 @@
         <v>2043</v>
       </c>
       <c r="D130" t="n">
-        <v>4285.714</v>
+        <v>3600</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>2044</v>
       </c>
       <c r="D131" t="n">
-        <v>4523.81</v>
+        <v>3720</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -24640,7 +24640,7 @@
         <v>2045</v>
       </c>
       <c r="D132" t="n">
-        <v>4761.905</v>
+        <v>3840</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -24663,7 +24663,7 @@
         <v>2046</v>
       </c>
       <c r="D133" t="n">
-        <v>5000</v>
+        <v>3960</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D280"/>
+  <dimension ref="A1:D303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30704,7 +30704,7 @@
         <v>2030</v>
       </c>
       <c r="D3" t="n">
-        <v>480</v>
+        <v>540</v>
       </c>
     </row>
     <row r="4">
@@ -30722,7 +30722,7 @@
         <v>2040</v>
       </c>
       <c r="D4" t="n">
-        <v>560</v>
+        <v>680</v>
       </c>
     </row>
     <row r="5">
@@ -30794,7 +30794,7 @@
         <v>2040</v>
       </c>
       <c r="D8" t="n">
-        <v>50.529</v>
+        <v>50.53</v>
       </c>
     </row>
     <row r="9">
@@ -31064,7 +31064,7 @@
         <v>2030</v>
       </c>
       <c r="D23" t="n">
-        <v>45</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="24">
@@ -31082,7 +31082,7 @@
         <v>2040</v>
       </c>
       <c r="D24" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
@@ -31136,7 +31136,7 @@
         <v>2030</v>
       </c>
       <c r="D27" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28">
@@ -31154,7 +31154,7 @@
         <v>2040</v>
       </c>
       <c r="D28" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29">
@@ -31280,7 +31280,7 @@
         <v>2030</v>
       </c>
       <c r="D35" t="n">
-        <v>600</v>
+        <v>750</v>
       </c>
     </row>
     <row r="36">
@@ -31298,7 +31298,7 @@
         <v>2040</v>
       </c>
       <c r="D36" t="n">
-        <v>700</v>
+        <v>850</v>
       </c>
     </row>
     <row r="37">
@@ -31928,7 +31928,7 @@
         <v>2030</v>
       </c>
       <c r="D71" t="n">
-        <v>2.077</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -31946,7 +31946,7 @@
         <v>2040</v>
       </c>
       <c r="D72" t="n">
-        <v>2.077</v>
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -32072,7 +32072,7 @@
         <v>2030</v>
       </c>
       <c r="D79" t="n">
-        <v>8</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="80">
@@ -32090,7 +32090,7 @@
         <v>2040</v>
       </c>
       <c r="D80" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="81">
@@ -32144,7 +32144,7 @@
         <v>2030</v>
       </c>
       <c r="D83" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
     </row>
     <row r="84">
@@ -32162,7 +32162,7 @@
         <v>2040</v>
       </c>
       <c r="D84" t="n">
-        <v>25</v>
+        <v>25.5</v>
       </c>
     </row>
     <row r="85">
@@ -32288,7 +32288,7 @@
         <v>2030</v>
       </c>
       <c r="D91" t="n">
-        <v>63</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="92">
@@ -32306,7 +32306,7 @@
         <v>2040</v>
       </c>
       <c r="D92" t="n">
-        <v>70</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="93">
@@ -32360,7 +32360,7 @@
         <v>2030</v>
       </c>
       <c r="D95" t="n">
-        <v>2.595</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="96">
@@ -32378,7 +32378,7 @@
         <v>2040</v>
       </c>
       <c r="D96" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -32432,7 +32432,7 @@
         <v>2030</v>
       </c>
       <c r="D99" t="n">
-        <v>8.319000000000001</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="100">
@@ -32450,7 +32450,7 @@
         <v>2040</v>
       </c>
       <c r="D100" t="n">
-        <v>9.319000000000001</v>
+        <v>12.6</v>
       </c>
     </row>
     <row r="101">
@@ -32504,7 +32504,7 @@
         <v>2030</v>
       </c>
       <c r="D103" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="104">
@@ -32522,7 +32522,7 @@
         <v>2040</v>
       </c>
       <c r="D104" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="105">
@@ -32576,7 +32576,7 @@
         <v>2030</v>
       </c>
       <c r="D107" t="n">
-        <v>15</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="108">
@@ -32594,7 +32594,7 @@
         <v>2040</v>
       </c>
       <c r="D108" t="n">
-        <v>25</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="109">
@@ -32936,7 +32936,7 @@
         <v>2030</v>
       </c>
       <c r="D127" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="128">
@@ -33008,7 +33008,7 @@
         <v>2030</v>
       </c>
       <c r="D131" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="132">
@@ -33026,7 +33026,7 @@
         <v>2040</v>
       </c>
       <c r="D132" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="133">
@@ -33224,7 +33224,7 @@
         <v>2030</v>
       </c>
       <c r="D143" t="n">
-        <v>280</v>
+        <v>357.7</v>
       </c>
     </row>
     <row r="144">
@@ -33242,7 +33242,7 @@
         <v>2040</v>
       </c>
       <c r="D144" t="n">
-        <v>330</v>
+        <v>408</v>
       </c>
     </row>
     <row r="145">
@@ -33368,7 +33368,7 @@
         <v>2030</v>
       </c>
       <c r="D151" t="n">
-        <v>24</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="152">
@@ -33512,7 +33512,7 @@
         <v>2030</v>
       </c>
       <c r="D159" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
     </row>
     <row r="160">
@@ -33530,7 +33530,7 @@
         <v>2040</v>
       </c>
       <c r="D160" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="161">
@@ -33584,7 +33584,7 @@
         <v>2030</v>
       </c>
       <c r="D163" t="n">
-        <v>75</v>
+        <v>76.3</v>
       </c>
     </row>
     <row r="164">
@@ -33602,7 +33602,7 @@
         <v>2040</v>
       </c>
       <c r="D164" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="165">
@@ -33656,7 +33656,7 @@
         <v>2030</v>
       </c>
       <c r="D167" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="168">
@@ -33674,7 +33674,7 @@
         <v>2040</v>
       </c>
       <c r="D168" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="169">
@@ -34034,7 +34034,7 @@
         <v>2040</v>
       </c>
       <c r="D188" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="189">
@@ -35456,7 +35456,7 @@
         <v>2030</v>
       </c>
       <c r="D267" t="n">
-        <v>29.4</v>
+        <v>59.3</v>
       </c>
     </row>
     <row r="268">
@@ -35474,7 +35474,7 @@
         <v>2040</v>
       </c>
       <c r="D268" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
     </row>
     <row r="269">
@@ -35528,7 +35528,7 @@
         <v>2030</v>
       </c>
       <c r="D271" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="272">
@@ -35546,7 +35546,7 @@
         <v>2040</v>
       </c>
       <c r="D272" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="273">
@@ -35600,7 +35600,7 @@
         <v>2030</v>
       </c>
       <c r="D275" t="n">
-        <v>152.2</v>
+        <v>171</v>
       </c>
     </row>
     <row r="276">
@@ -35618,7 +35618,7 @@
         <v>2040</v>
       </c>
       <c r="D276" t="n">
-        <v>205</v>
+        <v>224</v>
       </c>
     </row>
     <row r="277">
@@ -35691,6 +35691,420 @@
       </c>
       <c r="D280" t="n">
         <v>113.9</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D281" t="n">
+        <v>13.346</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D282" t="n">
+        <v>22.017</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D283" t="n">
+        <v>15.136</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D284" t="n">
+        <v>21.793</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D285" t="n">
+        <v>40.471</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D286" t="n">
+        <v>69.18899999999999</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D287" t="n">
+        <v>85.21299999999999</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D288" t="n">
+        <v>100.922</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D289" t="n">
+        <v>107.886</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D290" t="n">
+        <v>28.413</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D291" t="n">
+        <v>40.003</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D292" t="n">
+        <v>80.925</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D293" t="n">
+        <v>119.816</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D294" t="n">
+        <v>133.171</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D295" t="n">
+        <v>137.362</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C296" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D296" t="n">
+        <v>140.687</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C297" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D297" t="n">
+        <v>343.4</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C298" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D298" t="n">
+        <v>336.3</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C299" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D299" t="n">
+        <v>376.2</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C300" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D300" t="n">
+        <v>455.9</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C301" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D301" t="n">
+        <v>544.4</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C302" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D302" t="n">
+        <v>629.3</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C303" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D303" t="n">
+        <v>662.9</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -30646,7 +30646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D303"/>
+  <dimension ref="A1:D313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36105,6 +36105,186 @@
       </c>
       <c r="D303" t="n">
         <v>662.9</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C304" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D304" t="n">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C305" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D305" t="n">
+        <v>20.8</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C306" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D306" t="n">
+        <v>5.127</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C307" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D307" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C308" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D308" t="n">
+        <v>50.35</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C309" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D309" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C310" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D310" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C311" t="n">
+        <v>2023</v>
+      </c>
+      <c r="D311" t="n">
+        <v>4.04</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C312" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D312" t="n">
+        <v>5.43</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C313" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D313" t="n">
+        <v>5.333</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -30646,7 +30646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D313"/>
+  <dimension ref="A1:D326"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36285,6 +36285,240 @@
       </c>
       <c r="D313" t="n">
         <v>5.333</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>cap_coal_gw</t>
+        </is>
+      </c>
+      <c r="C314" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D314" t="n">
+        <v>1.756</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>cap_coal_gw</t>
+        </is>
+      </c>
+      <c r="C315" t="n">
+        <v>2021</v>
+      </c>
+      <c r="D315" t="n">
+        <v>1.756</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>cap_coal_gw</t>
+        </is>
+      </c>
+      <c r="C316" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D316" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>cap_coal_gw</t>
+        </is>
+      </c>
+      <c r="C317" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C318" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D318" t="n">
+        <v>4.606</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C319" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D319" t="n">
+        <v>4.433</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C320" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D320" t="n">
+        <v>4.395</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C321" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D321" t="n">
+        <v>4.373</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C322" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D322" t="n">
+        <v>4.485</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C323" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D323" t="n">
+        <v>4.645</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>cap_psp_gw</t>
+        </is>
+      </c>
+      <c r="C324" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D324" t="n">
+        <v>2.82</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>cap_psp_gw</t>
+        </is>
+      </c>
+      <c r="C325" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D325" t="n">
+        <v>3.707</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>cap_psp_gw</t>
+        </is>
+      </c>
+      <c r="C326" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D326" t="n">
+        <v>3.707</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -30646,7 +30646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D326"/>
+  <dimension ref="A1:D401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30740,7 +30740,7 @@
         <v>2050</v>
       </c>
       <c r="D5" t="n">
-        <v>640</v>
+        <v>760</v>
       </c>
     </row>
     <row r="6">
@@ -30794,7 +30794,7 @@
         <v>2040</v>
       </c>
       <c r="D8" t="n">
-        <v>50.53</v>
+        <v>60.929</v>
       </c>
     </row>
     <row r="9">
@@ -30812,7 +30812,7 @@
         <v>2050</v>
       </c>
       <c r="D9" t="n">
-        <v>17.712</v>
+        <v>51.586</v>
       </c>
     </row>
     <row r="10">
@@ -31316,7 +31316,7 @@
         <v>2050</v>
       </c>
       <c r="D37" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="38">
@@ -31928,7 +31928,7 @@
         <v>2030</v>
       </c>
       <c r="D71" t="n">
-        <v>2</v>
+        <v>2.077</v>
       </c>
     </row>
     <row r="72">
@@ -31946,7 +31946,7 @@
         <v>2040</v>
       </c>
       <c r="D72" t="n">
-        <v>2</v>
+        <v>2.077</v>
       </c>
     </row>
     <row r="73">
@@ -32360,7 +32360,7 @@
         <v>2030</v>
       </c>
       <c r="D95" t="n">
-        <v>1.2</v>
+        <v>2.595</v>
       </c>
     </row>
     <row r="96">
@@ -32378,7 +32378,7 @@
         <v>2040</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="97">
@@ -33260,7 +33260,7 @@
         <v>2050</v>
       </c>
       <c r="D145" t="n">
-        <v>380</v>
+        <v>450</v>
       </c>
     </row>
     <row r="146">
@@ -34034,7 +34034,7 @@
         <v>2040</v>
       </c>
       <c r="D188" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
@@ -34646,7 +34646,7 @@
         <v>2045</v>
       </c>
       <c r="D222" t="n">
-        <v>35.824</v>
+        <v>56.508</v>
       </c>
     </row>
     <row r="223">
@@ -36158,7 +36158,7 @@
         <v>2019</v>
       </c>
       <c r="D306" t="n">
-        <v>5.127</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="307">
@@ -36194,7 +36194,7 @@
         <v>2019</v>
       </c>
       <c r="D308" t="n">
-        <v>50.35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="309">
@@ -36230,7 +36230,7 @@
         <v>2030</v>
       </c>
       <c r="D310" t="n">
-        <v>90</v>
+        <v>58</v>
       </c>
     </row>
     <row r="311">
@@ -36374,7 +36374,7 @@
         <v>2019</v>
       </c>
       <c r="D318" t="n">
-        <v>4.606</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="319">
@@ -36410,7 +36410,7 @@
         <v>2050</v>
       </c>
       <c r="D320" t="n">
-        <v>4.395</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="321">
@@ -36428,7 +36428,7 @@
         <v>2019</v>
       </c>
       <c r="D321" t="n">
-        <v>4.373</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="322">
@@ -36464,7 +36464,7 @@
         <v>2050</v>
       </c>
       <c r="D323" t="n">
-        <v>4.645</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="324">
@@ -36519,6 +36519,1356 @@
       </c>
       <c r="D326" t="n">
         <v>3.707</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C327" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D327" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C328" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D328" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C329" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D329" t="n">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C330" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D330" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C331" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D331" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C332" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D332" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C333" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D333" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C334" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D334" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C335" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D335" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C336" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D336" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C337" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D337" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C338" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D338" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C339" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D339" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C340" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D340" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C341" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D341" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C342" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D342" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C343" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D343" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C344" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D344" t="n">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C345" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D345" t="n">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C346" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D346" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C347" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D347" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C348" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D348" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C349" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D349" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C350" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D350" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C351" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D351" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C352" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D352" t="n">
+        <v>21.5</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C353" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D353" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C354" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D354" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C355" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D355" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C356" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D356" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C357" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D357" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C358" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D358" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C359" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D359" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C360" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D360" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C361" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D361" t="n">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C362" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D362" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C363" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D363" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C364" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D364" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C365" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D365" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C366" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D366" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C367" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D367" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C368" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D368" t="n">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C369" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D369" t="n">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C370" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D370" t="n">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C371" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D371" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C372" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D372" t="n">
+        <v>24.5</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C373" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D373" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C374" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D374" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C375" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D375" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C376" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D376" t="n">
+        <v>9.199999999999999</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C377" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D377" t="n">
+        <v>13.4</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C378" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D378" t="n">
+        <v>15.6</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C379" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D379" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C380" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D380" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C381" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D381" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>cap_nuclear_gw</t>
+        </is>
+      </c>
+      <c r="C382" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D382" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C383" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D383" t="n">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C384" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D384" t="n">
+        <v>17.3</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C385" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D385" t="n">
+        <v>18.1</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C386" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D386" t="n">
+        <v>18.8</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C387" t="n">
+        <v>2019</v>
+      </c>
+      <c r="D387" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C388" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D388" t="n">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C389" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D389" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>AT_SI</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C390" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D390" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C391" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D391" t="n">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C392" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D392" t="n">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C393" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D393" t="n">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>cap_solar_gw</t>
+        </is>
+      </c>
+      <c r="C394" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D394" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C395" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D395" t="n">
+        <v>14.1</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>cap_wind_gw</t>
+        </is>
+      </c>
+      <c r="C396" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D396" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C397" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D397" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>cap_hydro_gw</t>
+        </is>
+      </c>
+      <c r="C398" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D398" t="n">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C399" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D399" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>cap_gas_gw</t>
+        </is>
+      </c>
+      <c r="C400" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D400" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>demand_twh</t>
+        </is>
+      </c>
+      <c r="C401" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D401" t="n">
+        <v>616</v>
       </c>
     </row>
   </sheetData>

--- a/scenarios.xlsx
+++ b/scenarios.xlsx
@@ -6325,7 +6325,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>101.6667</v>
+        <v>100.2175795992382</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -6348,7 +6348,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>104.3333</v>
+        <v>101.4351135398122</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>107</v>
+        <v>102.6526931390505</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>109.6667</v>
+        <v>103.8702727382887</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>112.3333</v>
+        <v>105.0878066788627</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>115</v>
+        <v>106.3053862781009</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -6463,7 +6463,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>117.6667</v>
+        <v>107.5229658773392</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>120.3333</v>
+        <v>108.7404998179131</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>123</v>
+        <v>109.9580794171514</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -6532,7 +6532,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>125.6667</v>
+        <v>111.1756590163896</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -6555,7 +6555,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>128.3333</v>
+        <v>112.3931929569636</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>131</v>
+        <v>113.6107725562018</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>133.6667</v>
+        <v>114.8283521554401</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -6624,7 +6624,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>136.3333</v>
+        <v>116.0458860960141</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -6647,7 +6647,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>139</v>
+        <v>117.2634656952523</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>141.6667</v>
+        <v>118.4810452944905</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>144.3333</v>
+        <v>119.6985792350645</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>147</v>
+        <v>120.9161588343028</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -6739,7 +6739,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>149.6667</v>
+        <v>122.133738433541</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -6762,7 +6762,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>152.3333</v>
+        <v>123.351272374115</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -6785,7 +6785,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>155</v>
+        <v>124.5688519733532</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -6831,7 +6831,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>100.4762</v>
+        <v>100.0621733628303</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>101.2381</v>
+        <v>100.4100467256606</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>102</v>
+        <v>100.7579200884909</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>102.762</v>
+        <v>101.1058391099855</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>103.5239</v>
+        <v>101.4537124728158</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>104.2856</v>
+        <v>101.8014945183177</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -6969,7 +6969,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>105.0476</v>
+        <v>102.1494135398122</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>105.8095</v>
+        <v>102.4972869026425</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>106.5714</v>
+        <v>102.8451602654729</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>107.3333</v>
+        <v>103.1930336283032</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>108.0952</v>
+        <v>103.5409069911335</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>108.8572</v>
+        <v>103.8888260126281</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -7107,7 +7107,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>109.6191</v>
+        <v>104.2366993754584</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -7130,7 +7130,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>110.381</v>
+        <v>104.5845727382887</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -7153,7 +7153,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>111.1429</v>
+        <v>104.932446101119</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>111.9047</v>
+        <v>105.2802738052851</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -7199,7 +7199,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>112.6666</v>
+        <v>105.6281471681154</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>113.4285</v>
+        <v>105.9760205309457</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>114.1904</v>
+        <v>106.323893893776</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -7268,7 +7268,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>114.9524</v>
+        <v>106.6718129152706</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>115.7143</v>
+        <v>107.0196862781009</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>100.7143</v>
+        <v>100.0932328735776</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>101.8572</v>
+        <v>100.6150657471552</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>103.0001</v>
+        <v>101.1368986207328</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -7406,7 +7406,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>104.1428</v>
+        <v>101.6586401769819</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -7429,7 +7429,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>105.2857</v>
+        <v>102.1804730505595</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -7452,7 +7452,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>106.4285</v>
+        <v>102.7022602654729</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>107.5714</v>
+        <v>103.2240931390505</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -7498,7 +7498,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>108.7143</v>
+        <v>103.745926012628</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>109.8572</v>
+        <v>104.2677588862057</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>111.0001</v>
+        <v>104.7895917597832</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>112.1428</v>
+        <v>105.3113333160324</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>113.2857</v>
+        <v>105.83316618961</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -7613,7 +7613,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>114.4285</v>
+        <v>106.3549534045233</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -7636,7 +7636,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>115.5714</v>
+        <v>106.8767862781009</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>116.7143</v>
+        <v>107.3986191516785</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>117.8572</v>
+        <v>107.9204520252561</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -7705,7 +7705,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>119.0001</v>
+        <v>108.4422848988337</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>120.1428</v>
+        <v>108.9640264550828</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -7751,7 +7751,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>121.2857</v>
+        <v>109.4858593286604</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>122.4285</v>
+        <v>110.0076465435738</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>123.5714</v>
+        <v>110.5294794171514</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>100.2381</v>
+        <v>100.0310595107473</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>100.6191</v>
+        <v>100.2050190214946</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>101</v>
+        <v>100.3789328735776</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>101.381</v>
+        <v>100.5528923843249</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>101.7619</v>
+        <v>100.7268062364079</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>102.1429</v>
+        <v>100.9007657471552</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>102.5239</v>
+        <v>101.0747252579025</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>102.9048</v>
+        <v>101.2486391099855</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -8027,7 +8027,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>103.2858</v>
+        <v>101.4225986207328</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>103.6667</v>
+        <v>101.5965124728158</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>104.0475</v>
+        <v>101.7703806662346</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>104.4285</v>
+        <v>101.9443401769819</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>104.8095</v>
+        <v>102.1182996877292</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>105.1904</v>
+        <v>102.2922135398122</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>105.5714</v>
+        <v>102.4661730505595</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -8188,7 +8188,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>105.9523</v>
+        <v>102.6400869026425</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>106.3333</v>
+        <v>102.8140464133898</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>106.7143</v>
+        <v>102.9880059241371</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>107.0952</v>
+        <v>103.1619197762201</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>107.4762</v>
+        <v>103.3358792869674</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -8303,7 +8303,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>107.8571</v>
+        <v>103.5097931390505</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4571428.5714</v>
+        <v>3966183.035706348</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -8919,7 +8919,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5828571.4287</v>
+        <v>4618080.357216407</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7085714.2858</v>
+        <v>5269977.678622754</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>8342857.1429</v>
+        <v>5921875.000029102</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>9599999.9999</v>
+        <v>6573772.321383594</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10857142.8572</v>
+        <v>7225669.642893652</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12114285.7143</v>
+        <v>7877566.9643</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13371428.5714</v>
+        <v>8529464.285706347</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -9080,7 +9080,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14628571.4287</v>
+        <v>9181361.607216407</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15885714.2858</v>
+        <v>9833258.928622752</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17142857.1429</v>
+        <v>10485156.2500291</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>18399999.9999</v>
+        <v>11137053.57138359</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>19657142.8572</v>
+        <v>11788950.89289365</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -9195,7 +9195,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>20914285.7143</v>
+        <v>12440848.2143</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>22171428.5714</v>
+        <v>13092745.53570635</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>23428571.4287</v>
+        <v>13744642.85721641</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>24685714.2858</v>
+        <v>14396540.17862275</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>25942857.1429</v>
+        <v>15048437.5000291</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>27199999.9999</v>
+        <v>15700334.82138359</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>28457142.8572</v>
+        <v>16352232.14289365</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29714285.7143</v>
+        <v>17004129.4643</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2476190.4762</v>
+        <v>2006208.147326367</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -11996,7 +11996,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3452380.9524</v>
+        <v>2512416.294652734</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4428571.4286</v>
+        <v>3018624.441979102</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -12042,7 +12042,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5404761.9048</v>
+        <v>3524832.589305469</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6380952.381</v>
+        <v>4031040.736631836</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7357142.8571</v>
+        <v>4537248.883906348</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -12111,7 +12111,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8333333.3333</v>
+        <v>5043457.031232715</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9309523.8095</v>
+        <v>5549665.178559082</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -12157,7 +12157,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10285714.2857</v>
+        <v>6055873.32588545</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11261904.7619</v>
+        <v>6562081.473211817</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12238095.2381</v>
+        <v>7068289.620538183</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13214285.7143</v>
+        <v>7574497.76786455</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -12249,7 +12249,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14190476.1905</v>
+        <v>8080705.915190918</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -12272,7 +12272,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15166666.6667</v>
+        <v>8586914.062517285</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -12295,7 +12295,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16142857.1429</v>
+        <v>9093122.209843652</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -12318,7 +12318,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17119047.619</v>
+        <v>9599330.357118163</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>18095238.0952</v>
+        <v>10105538.50444453</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -12364,7 +12364,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>19071428.5714</v>
+        <v>10611746.6517709</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -12387,7 +12387,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>20047619.0476</v>
+        <v>11117954.79909727</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -12410,7 +12410,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>21023809.5238</v>
+        <v>11624162.94642363</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -12433,7 +12433,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22000000</v>
+        <v>12130371.09375</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>380952.381</v>
+        <v>293833.7053818359</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>561904.7619</v>
+        <v>387667.4107118164</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>742857.1429</v>
+        <v>481501.1160936523</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>923809.5238</v>
+        <v>575334.8214236328</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1104761.9048</v>
+        <v>669168.5268054687</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1285714.2857</v>
+        <v>763002.2321354492</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -12617,7 +12617,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1466666.6667</v>
+        <v>856835.9375172851</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -12640,7 +12640,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1647619.0476</v>
+        <v>950669.6428472656</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -12663,7 +12663,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1828571.4286</v>
+        <v>1044503.348229102</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2009523.8095</v>
+        <v>1138337.053559082</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2190476.1905</v>
+        <v>1232170.758940918</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2371428.5714</v>
+        <v>1326004.464270898</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2552380.9524</v>
+        <v>1419838.169652734</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2733333.3333</v>
+        <v>1513671.874982715</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -12801,7 +12801,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2914285.7143</v>
+        <v>1607505.580364551</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -12824,7 +12824,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3095238.0952</v>
+        <v>1701339.285694531</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -12847,7 +12847,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>3276190.4762</v>
+        <v>1795172.991076367</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -12870,7 +12870,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3457142.8571</v>
+        <v>1889006.696406348</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3638095.2381</v>
+        <v>1982840.401788184</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>3819047.619</v>
+        <v>2076674.107118164</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -12939,7 +12939,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4000000</v>
+        <v>2170507.8125</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>33333.3333</v>
+        <v>22099.60935771484</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -13008,7 +13008,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>56666.6667</v>
+        <v>34199.21876728516</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -13031,7 +13031,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>80000</v>
+        <v>46298.828125</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -13054,7 +13054,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>103333.3333</v>
+        <v>58398.43748271484</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -13077,7 +13077,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>126666.6667</v>
+        <v>70498.04689228516</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -13100,7 +13100,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>150000</v>
+        <v>82597.65625</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -13123,7 +13123,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>173333.3333</v>
+        <v>94697.26560771484</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -13146,7 +13146,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>196666.6667</v>
+        <v>106796.8750172852</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>220000</v>
+        <v>118896.484375</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>243333.3333</v>
+        <v>130996.0937327148</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>266666.6667</v>
+        <v>143095.7031422851</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>290000</v>
+        <v>155195.3125</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>313333.3333</v>
+        <v>167294.9218577149</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -13284,7 +13284,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>336666.6667</v>
+        <v>179394.5312672851</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>360000</v>
+        <v>191494.140625</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>383333.3333</v>
+        <v>203593.7499827149</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>406666.6667</v>
+        <v>215693.3593922851</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>430000</v>
+        <v>227792.96875</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -13399,7 +13399,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>453333.3333</v>
+        <v>239892.5781077149</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -13422,7 +13422,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>476666.6667</v>
+        <v>251992.1875172851</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>500000</v>
+        <v>264091.796875</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -15050,7 +15050,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.667</v>
+        <v>0.5219086335158092</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -15073,7 +15073,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.6253</v>
+        <v>0.959455612909816</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -15096,7 +15096,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2.5835</v>
+        <v>1.396956933639585</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.5418</v>
+        <v>1.834503913033592</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.5</v>
+        <v>2.27200523376336</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -15165,7 +15165,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5.2</v>
+        <v>2.591615883430276</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.9</v>
+        <v>2.911226533097191</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.6</v>
+        <v>3.230837182764106</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -15234,7 +15234,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.3</v>
+        <v>3.550447832431021</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -15257,7 +15257,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>3.870058482097936</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8.199999999999999</v>
+        <v>3.961375810574198</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8.4</v>
+        <v>4.05269313905046</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8.6</v>
+        <v>4.144010467526721</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>8.800000000000001</v>
+        <v>4.235327796002983</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -15372,7 +15372,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>4.326645124479244</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9.166700000000001</v>
+        <v>4.402758117764209</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9.333299999999999</v>
+        <v>4.478825452384934</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -15441,7 +15441,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9.5</v>
+        <v>4.554938445669898</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -15464,7 +15464,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9.666700000000001</v>
+        <v>4.631051438954862</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9.833299999999999</v>
+        <v>4.707118773575588</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -15510,7 +15510,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>4.783231766860552</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.2381</v>
+        <v>0.9793265591019786</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1.7143</v>
+        <v>1.196753118203957</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.1905</v>
+        <v>1.414179677305936</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -16131,7 +16131,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.6667</v>
+        <v>1.631606236407914</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>3.1429</v>
+        <v>1.849032795509893</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -16177,7 +16177,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>3.6191</v>
+        <v>2.066459354611871</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -16200,7 +16200,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4.0953</v>
+        <v>2.283885913713851</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -16223,7 +16223,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4.5715</v>
+        <v>2.501312472815829</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5.0477</v>
+        <v>2.718739031917807</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -16269,7 +16269,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5.5239</v>
+        <v>2.936165591019787</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -16292,7 +16292,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5.9999</v>
+        <v>3.153500832793289</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -16315,7 +16315,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6.4761</v>
+        <v>3.370927391895267</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>6.9523</v>
+        <v>3.588353950997246</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>7.4285</v>
+        <v>3.805780510099225</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>7.9047</v>
+        <v>4.023207069201203</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8.3809</v>
+        <v>4.240633628303182</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>8.857100000000001</v>
+        <v>4.45806018740516</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>9.333299999999999</v>
+        <v>4.675486746507138</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>9.8095</v>
+        <v>4.892913305609117</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -16499,7 +16499,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.2857</v>
+        <v>5.110339864711095</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.7619</v>
+        <v>5.327766423813075</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D401"/>
+  <dimension ref="A1:D493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30686,7 +30686,7 @@
         <v>2025</v>
       </c>
       <c r="D2" t="n">
-        <v>460</v>
+        <v>441.5</v>
       </c>
     </row>
     <row r="3">
@@ -30704,7 +30704,7 @@
         <v>2030</v>
       </c>
       <c r="D3" t="n">
-        <v>540</v>
+        <v>474.9</v>
       </c>
     </row>
     <row r="4">
@@ -30722,7 +30722,7 @@
         <v>2040</v>
       </c>
       <c r="D4" t="n">
-        <v>680</v>
+        <v>538.5</v>
       </c>
     </row>
     <row r="5">
@@ -30740,7 +30740,7 @@
         <v>2050</v>
       </c>
       <c r="D5" t="n">
-        <v>760</v>
+        <v>590.1</v>
       </c>
     </row>
     <row r="6">
@@ -31640,7 +31640,7 @@
         <v>2030</v>
       </c>
       <c r="D55" t="n">
-        <v>15</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="56">
@@ -31658,7 +31658,7 @@
         <v>2040</v>
       </c>
       <c r="D56" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="57">
@@ -31676,7 +31676,7 @@
         <v>2050</v>
       </c>
       <c r="D57" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="58">
@@ -37868,7 +37868,1663 @@
         <v>2035</v>
       </c>
       <c r="D401" t="n">
-        <v>616</v>
+        <v>514</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C402" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D402" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C403" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D403" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C404" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D404" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C405" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D405" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C406" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D406" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C407" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D407" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C408" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D408" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C409" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D409" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C410" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D410" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C411" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D411" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C412" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D412" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C413" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D413" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C414" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D414" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C415" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D415" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C416" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D416" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C417" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D417" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C418" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D418" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C419" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D419" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C420" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D420" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C421" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D421" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C422" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D422" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C423" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D423" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C424" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D424" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C425" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D425" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C426" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D426" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C427" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D427" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C428" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D428" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C429" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D429" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C430" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D430" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C431" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D431" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C432" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D432" t="n">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>cap_flex_gw</t>
+        </is>
+      </c>
+      <c r="C433" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D433" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C434" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D434" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C435" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D435" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C436" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D436" t="n">
+        <v>11.25</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C437" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D437" t="n">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C438" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D438" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C439" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D439" t="n">
+        <v>21.56</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C440" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D440" t="n">
+        <v>33.12</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C441" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D441" t="n">
+        <v>33.12</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C442" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D442" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C443" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D443" t="n">
+        <v>1.88</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C444" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D444" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C445" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D445" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C446" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D446" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C447" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D447" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C448" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D448" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C449" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D449" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>IT_NORTH</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C450" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D450" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>IT_NORTH</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C451" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D451" t="n">
+        <v>5.62</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>IT_NORTH</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C452" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D452" t="n">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>IT_NORTH</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C453" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D453" t="n">
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C454" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D454" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C455" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D455" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C456" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D456" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C457" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D457" t="n">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>DE_REST</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C458" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D458" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>DE_REST</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C459" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D459" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>DE_REST</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C460" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D460" t="n">
+        <v>9.380000000000001</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>DE_REST</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C461" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D461" t="n">
+        <v>13.75</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C462" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D462" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C463" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D463" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C464" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D464" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C465" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D465" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C466" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D466" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C467" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D467" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C468" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D468" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C469" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D469" t="n">
+        <v>4.06</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C470" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D470" t="n">
+        <v>8.44</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C471" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D471" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C472" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D472" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>DK</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C473" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D473" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C474" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D474" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C475" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D475" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C476" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D476" t="n">
+        <v>8.75</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C477" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D477" t="n">
+        <v>25.94</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C478" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D478" t="n">
+        <v>29.38</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C479" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D479" t="n">
+        <v>29.38</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C480" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D480" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C481" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D481" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C482" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D482" t="n">
+        <v>3.44</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C483" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D483" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C484" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D484" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C485" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D485" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C486" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D486" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C487" t="n">
+        <v>2030</v>
+      </c>
+      <c r="D487" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C488" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D488" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C489" t="n">
+        <v>2040</v>
+      </c>
+      <c r="D489" t="n">
+        <v>3.75</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C490" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D490" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>PL_CZ</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C491" t="n">
+        <v>2050</v>
+      </c>
+      <c r="D491" t="n">
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C492" t="n">
+        <v>2035</v>
+      </c>
+      <c r="D492" t="n">
+        <v>25.94</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>DE_LU</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>cap_bess_gw</t>
+        </is>
+      </c>
+      <c r="C493" t="n">
+        <v>2045</v>
+      </c>
+      <c r="D493" t="n">
+        <v>33.12</v>
       </c>
     </row>
   </sheetData>
